--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/网络平面配置信息表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/网络平面配置信息表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,6 +818,186 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>参数面汇聚交换机</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>XH9330-128EO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>V100R001C020</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>64</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>参数面接入交换机</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>XH9930-128DQ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>V100R001C020</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>174</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>样本面-存储接入交换机</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>XH9930-128DQ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>V100R001C020</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>样本面-汇聚交换机</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>XH9930-128DQ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>V100R001C020</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>16</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>样本面-计算接入交换机</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>XH9930-128DQ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>V100R001C020</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>22</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/网络平面配置信息表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/网络平面配置信息表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -998,6 +998,186 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>参数面汇聚交换机</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>XH9330-128EO</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>V100R001C020</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>64</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>参数面接入交换机</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>XH9930-128DQ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>V100R001C020</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>174</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>样本面-存储接入交换机</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>XH9930-128DQ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>V100R001C020</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>样本面-汇聚交换机</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>XH9930-128DQ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>V100R001C020</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>16</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>样本面-计算接入交换机</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>XH9930-128DQ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>V100R001C020</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>22</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/网络平面配置信息表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/网络平面配置信息表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1178,6 +1178,186 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>参数面汇聚交换机</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>XH9330-128EO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>V100R001C020</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>64</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>参数面接入交换机</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>XH9930-128DQ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>V100R001C020</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>174</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>样本面-存储接入交换机</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>XH9930-128DQ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>V100R001C020</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>样本面-汇聚交换机</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>XH9930-128DQ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>V100R001C020</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>16</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>样本面-计算接入交换机</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>XH9930-128DQ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>V100R001C020</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>22</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>人工录入</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
